--- a/Vendas.xlsx
+++ b/Vendas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cursos\2026\TOTVS-EngenhariaDados e ML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070E4E08-12FD-4355-9B5A-6778E248F07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A70C65F1-EC17-4DB8-8807-F5F3D14FD5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{623A0F83-BF71-4EFA-88E7-EDBF8DFA9D99}"/>
   </bookViews>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId5"/>
+    <pivotCache cacheId="10" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="32">
   <si>
     <t>Paleta de Cores</t>
   </si>
@@ -65,9 +65,6 @@
   </si>
   <si>
     <t>Menus</t>
-  </si>
-  <si>
-    <t>ícones</t>
   </si>
   <si>
     <t>Grafico</t>
@@ -104,9 +101,6 @@
   </si>
   <si>
     <t>Etapa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voley </t>
   </si>
   <si>
     <t>Valor Unitário</t>
@@ -154,7 +148,10 @@
     <t>FILTRO</t>
   </si>
   <si>
-    <t>VENDAS JOGOS VOLEY OLIMPÍADAS</t>
+    <t>VENDAS JOGOS VOLEI OLIMPÍADAS</t>
+  </si>
+  <si>
+    <t>Volei</t>
   </si>
 </sst>
 </file>
@@ -301,100 +298,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Título 1" xfId="1" builtinId="16"/>
   </cellStyles>
-  <dxfs count="34">
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
@@ -1292,7 +1205,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2280,8 +2193,8 @@
       <xdr:row>15</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="2" name="Etapa">
@@ -2304,7 +2217,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -2363,8 +2276,8 @@
       <xdr:row>17</xdr:row>
       <xdr:rowOff>27214</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="2" name="Etapa 1">
@@ -2387,7 +2300,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -2753,6 +2666,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t> R$ 29.440.750,00 </a:t>
           </a:fld>
           <a:endParaRPr lang="pt-BR" sz="6000">
@@ -3139,7 +3053,140 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FF4B53CE-58B6-40B1-8D56-505E56164E9B}" name="Tabela dinâmica3" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B58EB9D4-4586-41E5-A4E4-9CE3638690B9}" name="Tabela dinâmica2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="A3:D7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="20" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Soma de Arrecadação" fld="9" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="1">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="0">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="8" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FF4B53CE-58B6-40B1-8D56-505E56164E9B}" name="Tabela dinâmica3" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A11:D15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -3204,150 +3251,17 @@
     <dataField name="Soma de Arrecadação" fld="9" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="31">
+    <format dxfId="3">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="28">
+    <format dxfId="2">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B58EB9D4-4586-41E5-A4E4-9CE3638690B9}" name="Tabela dinâmica2" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="A3:D7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="20" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Soma de Arrecadação" fld="9" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="30">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="29">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="8" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="9" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -3397,8 +3311,8 @@
     <tableColumn id="1" xr3:uid="{CC28CF7F-2593-4E16-BB0C-07E65710D429}" name="Esporte"/>
     <tableColumn id="2" xr3:uid="{288152C7-0E2E-4164-BDD1-5F02E033F28C}" name="Modalidade"/>
     <tableColumn id="3" xr3:uid="{19387D01-4040-4B6A-9E22-AC59EFE78F66}" name="Etapa"/>
-    <tableColumn id="4" xr3:uid="{D84EE1A9-B073-4551-A302-E1CFEF24DADE}" name="Data" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{0BF17F69-F387-4005-BE82-2138408C9337}" name="Hora" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{D84EE1A9-B073-4551-A302-E1CFEF24DADE}" name="Data" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{0BF17F69-F387-4005-BE82-2138408C9337}" name="Hora" dataDxfId="4"/>
     <tableColumn id="6" xr3:uid="{5DACC306-97B9-4F92-A956-691D0F2D54C4}" name="Local"/>
     <tableColumn id="7" xr3:uid="{672A6276-6D82-4437-AAD7-DDFAD1981134}" name="Total Ingressos"/>
     <tableColumn id="8" xr3:uid="{71C66B76-B7AF-47CC-BE3D-A5846C15C43C}" name="Total vendido"/>
@@ -3728,10 +3642,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF318C49-A970-44EF-8551-D552F1D5767B}">
-  <dimension ref="A2:K20"/>
+  <dimension ref="A2:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:11" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3742,38 +3656,38 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="19"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="18"/>
       <c r="B7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -3781,13 +3695,8 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="I11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -3796,7 +3705,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -3805,7 +3714,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -3814,7 +3723,7 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -3823,7 +3732,7 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -3893,45 +3802,45 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" t="s">
-        <v>17</v>
-      </c>
       <c r="J1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
         <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
       </c>
       <c r="D2" s="7">
         <v>45832</v>
@@ -3940,7 +3849,7 @@
         <v>0.375</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G2">
         <v>30000</v>
@@ -3952,19 +3861,19 @@
         <v>150</v>
       </c>
       <c r="J2">
-        <f>I2*H2</f>
+        <f t="shared" ref="J2:J23" si="0">I2*H2</f>
         <v>3000000</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
       </c>
       <c r="D3" s="7">
         <v>45832</v>
@@ -3973,7 +3882,7 @@
         <v>0.5</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G3">
         <v>30000</v>
@@ -3985,19 +3894,19 @@
         <v>150</v>
       </c>
       <c r="J3">
-        <f>I3*H3</f>
+        <f t="shared" si="0"/>
         <v>3150000</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
         <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
       </c>
       <c r="D4" s="7">
         <v>45832</v>
@@ -4006,7 +3915,7 @@
         <v>0.625</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G4">
         <v>30000</v>
@@ -4018,19 +3927,19 @@
         <v>150</v>
       </c>
       <c r="J4">
-        <f>I4*H4</f>
+        <f t="shared" si="0"/>
         <v>2970000</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
         <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
       </c>
       <c r="D5" s="7">
         <v>45832</v>
@@ -4039,7 +3948,7 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G5">
         <v>30000</v>
@@ -4051,19 +3960,19 @@
         <v>150</v>
       </c>
       <c r="J5">
-        <f>I5*H5</f>
+        <f t="shared" si="0"/>
         <v>4350000</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
       </c>
       <c r="D6" s="7">
         <v>45836</v>
@@ -4072,7 +3981,7 @@
         <v>0.375</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G6">
         <v>28000</v>
@@ -4084,19 +3993,19 @@
         <v>150</v>
       </c>
       <c r="J6">
-        <f>I6*H6</f>
+        <f t="shared" si="0"/>
         <v>3900000</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
         <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
       </c>
       <c r="D7" s="7">
         <v>45836</v>
@@ -4105,7 +4014,7 @@
         <v>0.5</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G7">
         <v>28000</v>
@@ -4117,19 +4026,19 @@
         <v>150</v>
       </c>
       <c r="J7">
-        <f>I7*H7</f>
+        <f t="shared" si="0"/>
         <v>3450000</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
         <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
       </c>
       <c r="D8" s="7">
         <v>45836</v>
@@ -4138,7 +4047,7 @@
         <v>0.625</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G8">
         <v>28000</v>
@@ -4150,19 +4059,19 @@
         <v>150</v>
       </c>
       <c r="J8">
-        <f>I8*H8</f>
+        <f t="shared" si="0"/>
         <v>2400000</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
         <v>13</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
       </c>
       <c r="D9" s="7">
         <v>45836</v>
@@ -4171,7 +4080,7 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G9">
         <v>28000</v>
@@ -4183,19 +4092,19 @@
         <v>150</v>
       </c>
       <c r="J9">
-        <f>I9*H9</f>
+        <f t="shared" si="0"/>
         <v>3300000</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D10" s="7">
         <v>45838</v>
@@ -4204,7 +4113,7 @@
         <v>0.375</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G10">
         <v>30000</v>
@@ -4216,19 +4125,19 @@
         <v>180</v>
       </c>
       <c r="J10">
-        <f>I10*H10</f>
+        <f t="shared" si="0"/>
         <v>3699000</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D11" s="7">
         <v>45838</v>
@@ -4237,7 +4146,7 @@
         <v>0.625</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G11">
         <v>28000</v>
@@ -4249,19 +4158,19 @@
         <v>180</v>
       </c>
       <c r="J11">
-        <f>I11*H11</f>
+        <f t="shared" si="0"/>
         <v>2700000</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D12" s="7">
         <v>45848</v>
@@ -4270,7 +4179,7 @@
         <v>0.625</v>
       </c>
       <c r="F12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G12">
         <v>30000</v>
@@ -4282,19 +4191,19 @@
         <v>250</v>
       </c>
       <c r="J12">
-        <f>I12*H12</f>
+        <f t="shared" si="0"/>
         <v>7175000</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" s="7">
         <v>45831</v>
@@ -4303,7 +4212,7 @@
         <v>0.375</v>
       </c>
       <c r="F13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G13">
         <v>30000</v>
@@ -4315,19 +4224,19 @@
         <v>150</v>
       </c>
       <c r="J13">
-        <f>I13*H13</f>
+        <f t="shared" si="0"/>
         <v>3225000</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D14" s="7">
         <v>45831</v>
@@ -4336,7 +4245,7 @@
         <v>0.5</v>
       </c>
       <c r="F14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G14">
         <v>30000</v>
@@ -4348,19 +4257,19 @@
         <v>150</v>
       </c>
       <c r="J14">
-        <f>I14*H14</f>
+        <f t="shared" si="0"/>
         <v>2775000</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15" s="7">
         <v>45831</v>
@@ -4369,7 +4278,7 @@
         <v>0.625</v>
       </c>
       <c r="F15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G15">
         <v>30000</v>
@@ -4381,19 +4290,19 @@
         <v>150</v>
       </c>
       <c r="J15">
-        <f>I15*H15</f>
+        <f t="shared" si="0"/>
         <v>3135000</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D16" s="7">
         <v>45831</v>
@@ -4402,7 +4311,7 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G16">
         <v>30000</v>
@@ -4414,19 +4323,19 @@
         <v>150</v>
       </c>
       <c r="J16">
-        <f>I16*H16</f>
+        <f t="shared" si="0"/>
         <v>3716250</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D17" s="7">
         <v>45835</v>
@@ -4435,7 +4344,7 @@
         <v>0.375</v>
       </c>
       <c r="F17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G17">
         <v>28000</v>
@@ -4447,19 +4356,19 @@
         <v>150</v>
       </c>
       <c r="J17">
-        <f>I17*H17</f>
+        <f t="shared" si="0"/>
         <v>3075000</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D18" s="7">
         <v>45835</v>
@@ -4468,7 +4377,7 @@
         <v>0.5</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G18">
         <v>28000</v>
@@ -4480,19 +4389,19 @@
         <v>150</v>
       </c>
       <c r="J18">
-        <f>I18*H18</f>
+        <f t="shared" si="0"/>
         <v>3877500</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D19" s="7">
         <v>45835</v>
@@ -4501,7 +4410,7 @@
         <v>0.625</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G19">
         <v>28000</v>
@@ -4513,19 +4422,19 @@
         <v>150</v>
       </c>
       <c r="J19">
-        <f>I19*H19</f>
+        <f t="shared" si="0"/>
         <v>1200000</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D20" s="7">
         <v>45835</v>
@@ -4534,7 +4443,7 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G20">
         <v>28000</v>
@@ -4546,19 +4455,19 @@
         <v>150</v>
       </c>
       <c r="J20">
-        <f>I20*H20</f>
+        <f t="shared" si="0"/>
         <v>1650000</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D21" s="7">
         <v>46202</v>
@@ -4567,7 +4476,7 @@
         <v>0.375</v>
       </c>
       <c r="F21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G21">
         <v>30000</v>
@@ -4579,19 +4488,19 @@
         <v>180</v>
       </c>
       <c r="J21">
-        <f>I21*H21</f>
+        <f t="shared" si="0"/>
         <v>1849500</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D22" s="7">
         <v>45838</v>
@@ -4600,7 +4509,7 @@
         <v>0.625</v>
       </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G22">
         <v>28000</v>
@@ -4612,19 +4521,19 @@
         <v>180</v>
       </c>
       <c r="J22">
-        <f>I22*H22</f>
+        <f t="shared" si="0"/>
         <v>1350000</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D23" s="7">
         <v>45847</v>
@@ -4633,7 +4542,7 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F23" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G23">
         <v>30000</v>
@@ -4645,7 +4554,7 @@
         <v>250</v>
       </c>
       <c r="J23">
-        <f>I23*H23</f>
+        <f t="shared" si="0"/>
         <v>3587500</v>
       </c>
     </row>
@@ -4670,34 +4579,34 @@
   <sheetData>
     <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" s="12">
         <v>24344000</v>
@@ -4711,7 +4620,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" s="12">
         <v>15750000</v>
@@ -4725,7 +4634,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B7" s="12">
         <v>40094000</v>
@@ -4748,34 +4657,34 @@
     </row>
     <row r="10" spans="1:8" ht="21" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="12">
         <v>24344000</v>
@@ -4789,7 +4698,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B14" s="12">
         <v>18288250</v>
@@ -4803,7 +4712,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B15" s="12">
         <v>42632250</v>
@@ -4839,20 +4748,20 @@
   <sheetData>
     <row r="2" spans="1:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
+        <v>29</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
